--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/post DFS_HRM-2031-0432/Panel-28/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/post DFS_HRM-2031-0432/Panel-28/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Back_Summary.xlsx
@@ -413,410 +413,526 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Measured by operator 7 on tool HRM-2</t>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>17.16024</v>
+      </c>
+      <c r="D2" t="n">
+        <v>16.47423</v>
+      </c>
+      <c r="E2" t="n">
+        <v>16.64602</v>
+      </c>
+      <c r="F2" t="n">
+        <v>43.46516</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.05136</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.86795</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Pad 1</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.99349</v>
+        <v>17.15974</v>
       </c>
       <c r="D3" t="n">
-        <v>17.10946</v>
+        <v>16.59323</v>
       </c>
       <c r="E3" t="n">
-        <v>17.0748</v>
+        <v>16.95963</v>
       </c>
       <c r="F3" t="n">
-        <v>43.27605</v>
+        <v>42.42383</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05058</v>
+        <v>0.05184</v>
       </c>
       <c r="H3" t="n">
-        <v>1.85957</v>
+        <v>1.85175</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.84583</v>
+        <v>17.02598</v>
       </c>
       <c r="D4" t="n">
-        <v>16.79787</v>
+        <v>16.7994</v>
       </c>
       <c r="E4" t="n">
-        <v>17.07166</v>
+        <v>16.92814</v>
       </c>
       <c r="F4" t="n">
-        <v>42.93627</v>
+        <v>43.22819</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0508</v>
+        <v>0.04964</v>
       </c>
       <c r="H4" t="n">
-        <v>1.85482</v>
+        <v>1.83749</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.02543</v>
+        <v>17.15883</v>
       </c>
       <c r="D5" t="n">
-        <v>16.78518</v>
+        <v>16.64008</v>
       </c>
       <c r="E5" t="n">
-        <v>16.99725</v>
+        <v>16.81001</v>
       </c>
       <c r="F5" t="n">
-        <v>43.4206</v>
+        <v>42.17021</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05171</v>
+        <v>0.05129</v>
       </c>
       <c r="H5" t="n">
-        <v>1.84845</v>
+        <v>1.85551</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.92482</v>
+        <v>17.13209</v>
       </c>
       <c r="D6" t="n">
-        <v>16.63378</v>
+        <v>16.75971</v>
       </c>
       <c r="E6" t="n">
-        <v>16.83142</v>
+        <v>16.94799</v>
       </c>
       <c r="F6" t="n">
-        <v>42.34272</v>
+        <v>43.57892</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05091</v>
+        <v>0.05097</v>
       </c>
       <c r="H6" t="n">
-        <v>1.84658</v>
+        <v>1.84553</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.49453</v>
+        <v>17.64909</v>
       </c>
       <c r="D7" t="n">
-        <v>17.06973</v>
+        <v>16.84088</v>
       </c>
       <c r="E7" t="n">
-        <v>16.90213</v>
+        <v>17.4331</v>
       </c>
       <c r="F7" t="n">
-        <v>42.511</v>
+        <v>42.68271</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05185</v>
+        <v>0.05176</v>
       </c>
       <c r="H7" t="n">
-        <v>1.78849</v>
+        <v>1.82554</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.92727</v>
+        <v>16.71707</v>
       </c>
       <c r="D8" t="n">
-        <v>16.98652</v>
+        <v>16.3659</v>
       </c>
       <c r="E8" t="n">
-        <v>16.82736</v>
+        <v>16.67745</v>
       </c>
       <c r="F8" t="n">
-        <v>42.88</v>
+        <v>42.84575</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05112</v>
+        <v>0.05003</v>
       </c>
       <c r="H8" t="n">
-        <v>1.83196</v>
+        <v>1.8035</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.83892</v>
+        <v>16.93857</v>
       </c>
       <c r="D9" t="n">
-        <v>16.42455</v>
+        <v>16.70216</v>
       </c>
       <c r="E9" t="n">
-        <v>17.11749</v>
+        <v>16.87644</v>
       </c>
       <c r="F9" t="n">
-        <v>43.67314</v>
+        <v>43.75932</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05128</v>
+        <v>0.05136</v>
       </c>
       <c r="H9" t="n">
-        <v>1.83684</v>
+        <v>1.87344</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.13706</v>
+        <v>16.92027</v>
       </c>
       <c r="D10" t="n">
-        <v>16.87348</v>
+        <v>16.75414</v>
       </c>
       <c r="E10" t="n">
-        <v>17.01359</v>
+        <v>16.80027</v>
       </c>
       <c r="F10" t="n">
-        <v>42.9422</v>
+        <v>43.51151</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05039</v>
+        <v>0.05081</v>
       </c>
       <c r="H10" t="n">
-        <v>1.85083</v>
+        <v>1.85649</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>16.93406</v>
-      </c>
-      <c r="D11" t="n">
-        <v>16.92014</v>
-      </c>
-      <c r="E11" t="n">
-        <v>16.55267</v>
-      </c>
-      <c r="F11" t="n">
-        <v>42.34458</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.05225</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.88119</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pad 1</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>17.23968</v>
+      </c>
+      <c r="D12" t="n">
+        <v>16.75676</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.83774</v>
+      </c>
+      <c r="F12" t="n">
+        <v>43.42514</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.05013</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.83581</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>via 1</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.60902</v>
+        <v>17.12181</v>
       </c>
       <c r="D13" t="n">
-        <v>1.11998</v>
+        <v>16.986</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16.99986</v>
+      </c>
+      <c r="F13" t="n">
+        <v>43.28065</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.05116</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.84842</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.6039600000000001</v>
+        <v>17.2242</v>
       </c>
       <c r="D14" t="n">
-        <v>1.11522</v>
+        <v>16.82567</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.94841</v>
+      </c>
+      <c r="F14" t="n">
+        <v>41.91239</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.05039</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.8191</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.60808</v>
+        <v>16.8775</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1313</v>
+        <v>16.2583</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16.8463</v>
+      </c>
+      <c r="F15" t="n">
+        <v>42.50977</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.05069</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.84784</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.6085199999999999</v>
+        <v>17.22261</v>
       </c>
       <c r="D16" t="n">
-        <v>1.12811</v>
+        <v>16.74498</v>
+      </c>
+      <c r="E16" t="n">
+        <v>17.00421</v>
+      </c>
+      <c r="F16" t="n">
+        <v>43.87171</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.0508</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.85961</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.61061</v>
+        <v>17.19807</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1141</v>
+        <v>16.60885</v>
+      </c>
+      <c r="E17" t="n">
+        <v>16.92156</v>
+      </c>
+      <c r="F17" t="n">
+        <v>44.13206</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.05059</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.82901</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.63282</v>
+        <v>17.08832</v>
       </c>
       <c r="D18" t="n">
-        <v>1.14339</v>
+        <v>16.44838</v>
+      </c>
+      <c r="E18" t="n">
+        <v>17.00172</v>
+      </c>
+      <c r="F18" t="n">
+        <v>43.44529</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.05064</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.85162</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.62226</v>
+        <v>17.07869</v>
       </c>
       <c r="D19" t="n">
-        <v>1.12195</v>
+        <v>16.82444</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.89613</v>
+      </c>
+      <c r="F19" t="n">
+        <v>43.12641</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.0508</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.835</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.61217</v>
+        <v>17.17596</v>
       </c>
       <c r="D20" t="n">
-        <v>1.10458</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0.6039600000000001</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1.13212</v>
+        <v>16.68473</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.74787</v>
+      </c>
+      <c r="F20" t="n">
+        <v>43.5011</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.05192</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.81992</v>
       </c>
     </row>
   </sheetData>
